--- a/output/roomself_excel/11436.xlsx
+++ b/output/roomself_excel/11436.xlsx
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>179088</v>
+        <v>70021</v>
       </c>
       <c r="D2" t="n">
-        <v>3424</v>
+        <v>2276</v>
       </c>
       <c r="E2" t="n">
-        <v>522</v>
+        <v>373</v>
       </c>
       <c r="F2" t="n">
-        <v>394</v>
+        <v>256</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>121676</v>
+        <v>21614</v>
       </c>
       <c r="D3" t="n">
-        <v>3244</v>
+        <v>1236</v>
       </c>
       <c r="E3" t="n">
-        <v>434</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>401446</v>
+        <v>179088</v>
       </c>
       <c r="D4" t="n">
-        <v>6568</v>
+        <v>3424</v>
       </c>
       <c r="E4" t="n">
-        <v>918</v>
+        <v>522</v>
       </c>
       <c r="F4" t="n">
-        <v>812</v>
+        <v>394</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>127953</v>
+        <v>121676</v>
       </c>
       <c r="D5" t="n">
-        <v>3352</v>
+        <v>3244</v>
       </c>
       <c r="E5" t="n">
-        <v>412</v>
+        <v>434</v>
       </c>
       <c r="F5" t="n">
-        <v>28</v>
+        <v>375</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16112</v>
+        <v>96278</v>
       </c>
       <c r="D6" t="n">
-        <v>1032</v>
+        <v>2484</v>
       </c>
       <c r="E6" t="n">
-        <v>150</v>
+        <v>352</v>
       </c>
       <c r="F6" t="n">
-        <v>13</v>
+        <v>329</v>
       </c>
     </row>
     <row r="7">
@@ -576,14 +576,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6120</v>
+        <v>16112</v>
       </c>
       <c r="D7" t="n">
-        <v>628</v>
+        <v>1032</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5904</v>
+        <v>41652</v>
       </c>
       <c r="D8" t="n">
-        <v>684</v>
+        <v>1648</v>
       </c>
       <c r="E8" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -620,14 +620,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4512</v>
+        <v>10560</v>
       </c>
       <c r="D9" t="n">
-        <v>568</v>
+        <v>848</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -652,10 +652,10 @@
         <v>1904</v>
       </c>
       <c r="E10" t="n">
-        <v>233</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>70021</v>
+        <v>26069</v>
       </c>
       <c r="D11" t="n">
-        <v>2276</v>
+        <v>1320</v>
       </c>
       <c r="E11" t="n">
-        <v>373</v>
+        <v>110</v>
       </c>
       <c r="F11" t="n">
-        <v>256</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>96278</v>
+        <v>5670</v>
       </c>
       <c r="D12" t="n">
-        <v>2484</v>
+        <v>604</v>
       </c>
       <c r="E12" t="n">
-        <v>352</v>
+        <v>81</v>
       </c>
       <c r="F12" t="n">
-        <v>329</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13">
@@ -708,14 +708,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>11778</v>
+        <v>13664</v>
       </c>
       <c r="D13" t="n">
-        <v>916</v>
+        <v>936</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -730,20 +730,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>33475</v>
+        <v>26865</v>
       </c>
       <c r="D14" t="n">
-        <v>2000</v>
+        <v>1336</v>
       </c>
       <c r="E14" t="n">
-        <v>185</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -752,20 +752,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>20311</v>
+        <v>30450</v>
       </c>
       <c r="D15" t="n">
-        <v>1532</v>
+        <v>1412</v>
       </c>
       <c r="E15" t="n">
-        <v>193</v>
+        <v>150</v>
       </c>
       <c r="F15" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -774,20 +774,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>13664</v>
+        <v>115517</v>
       </c>
       <c r="D16" t="n">
-        <v>936</v>
+        <v>2816</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>446</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>312</v>
       </c>
     </row>
     <row r="17">
@@ -800,16 +800,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17480</v>
+        <v>401446</v>
       </c>
       <c r="D17" t="n">
-        <v>1128</v>
+        <v>6568</v>
       </c>
       <c r="E17" t="n">
-        <v>92</v>
+        <v>918</v>
       </c>
       <c r="F17" t="n">
-        <v>30</v>
+        <v>812</v>
       </c>
     </row>
     <row r="18">
@@ -822,16 +822,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>49704</v>
+        <v>127953</v>
       </c>
       <c r="D18" t="n">
-        <v>1916</v>
+        <v>3352</v>
       </c>
       <c r="E18" t="n">
-        <v>355</v>
+        <v>412</v>
       </c>
       <c r="F18" t="n">
-        <v>182</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19">
@@ -840,20 +840,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>115517</v>
+        <v>6120</v>
       </c>
       <c r="D19" t="n">
-        <v>2816</v>
+        <v>628</v>
       </c>
       <c r="E19" t="n">
-        <v>446</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>312</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -866,16 +866,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>34398</v>
+        <v>5904</v>
       </c>
       <c r="D20" t="n">
-        <v>1524</v>
+        <v>684</v>
       </c>
       <c r="E20" t="n">
-        <v>234</v>
+        <v>48</v>
       </c>
       <c r="F20" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -888,16 +888,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>123708</v>
+        <v>4512</v>
       </c>
       <c r="D21" t="n">
-        <v>2816</v>
+        <v>568</v>
       </c>
       <c r="E21" t="n">
-        <v>394</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>363</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -906,14 +906,14 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>41652</v>
+        <v>11778</v>
       </c>
       <c r="D22" t="n">
-        <v>1648</v>
+        <v>916</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -928,20 +928,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>26865</v>
+        <v>33475</v>
       </c>
       <c r="D23" t="n">
-        <v>1336</v>
+        <v>2000</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24">
@@ -950,20 +950,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>21614</v>
+        <v>20311</v>
       </c>
       <c r="D24" t="n">
-        <v>1236</v>
+        <v>1532</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>193</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25">
@@ -972,20 +972,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>26069</v>
+        <v>17480</v>
       </c>
       <c r="D25" t="n">
-        <v>1320</v>
+        <v>1128</v>
       </c>
       <c r="E25" t="n">
-        <v>413</v>
+        <v>92</v>
       </c>
       <c r="F25" t="n">
-        <v>139</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26">
@@ -998,16 +998,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3290</v>
+        <v>49704</v>
       </c>
       <c r="D26" t="n">
-        <v>468</v>
+        <v>1916</v>
       </c>
       <c r="E26" t="n">
-        <v>47</v>
+        <v>355</v>
       </c>
       <c r="F26" t="n">
-        <v>28</v>
+        <v>182</v>
       </c>
     </row>
     <row r="27">
@@ -1016,20 +1016,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>5670</v>
+        <v>34398</v>
       </c>
       <c r="D27" t="n">
-        <v>604</v>
+        <v>1524</v>
       </c>
       <c r="E27" t="n">
-        <v>81</v>
+        <v>234</v>
       </c>
       <c r="F27" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28">
@@ -1038,20 +1038,20 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>30450</v>
+        <v>123708</v>
       </c>
       <c r="D28" t="n">
-        <v>1412</v>
+        <v>2816</v>
       </c>
       <c r="E28" t="n">
-        <v>150</v>
+        <v>394</v>
       </c>
       <c r="F28" t="n">
-        <v>29</v>
+        <v>363</v>
       </c>
     </row>
     <row r="29">
@@ -1064,16 +1064,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>16500</v>
+        <v>3290</v>
       </c>
       <c r="D29" t="n">
-        <v>1040</v>
+        <v>468</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30">
@@ -1086,10 +1086,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>4640</v>
+        <v>16500</v>
       </c>
       <c r="D30" t="n">
-        <v>552</v>
+        <v>1040</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -1104,20 +1104,20 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>10560</v>
+        <v>4640</v>
       </c>
       <c r="D31" t="n">
-        <v>848</v>
+        <v>552</v>
       </c>
       <c r="E31" t="n">
-        <v>261</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">

--- a/output/roomself_excel/11436.xlsx
+++ b/output/roomself_excel/11436.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,47 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
         </is>
       </c>
     </row>
@@ -475,12 +510,31 @@
       <c r="D2" t="n">
         <v>2276</v>
       </c>
-      <c r="E2" t="n">
-        <v>373</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>256</v>
-      </c>
+        <v>343</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>226</v>
+      </c>
+      <c r="J2" t="n">
+        <v>30</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +551,15 @@
       <c r="D3" t="n">
         <v>1236</v>
       </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +576,31 @@
       <c r="D4" t="n">
         <v>3424</v>
       </c>
-      <c r="E4" t="n">
-        <v>522</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>394</v>
-      </c>
+        <v>492</v>
+      </c>
+      <c r="G4" t="n">
+        <v>30</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>364</v>
+      </c>
+      <c r="J4" t="n">
+        <v>30</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +617,31 @@
       <c r="D5" t="n">
         <v>3244</v>
       </c>
-      <c r="E5" t="n">
-        <v>434</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>375</v>
-      </c>
+        <v>345</v>
+      </c>
+      <c r="G5" t="n">
+        <v>30</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>404</v>
+      </c>
+      <c r="J5" t="n">
+        <v>30</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +658,31 @@
       <c r="D6" t="n">
         <v>2484</v>
       </c>
-      <c r="E6" t="n">
-        <v>352</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>329</v>
-      </c>
+        <v>322</v>
+      </c>
+      <c r="G6" t="n">
+        <v>30</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>299</v>
+      </c>
+      <c r="J6" t="n">
+        <v>30</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +699,15 @@
       <c r="D7" t="n">
         <v>1032</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +724,15 @@
       <c r="D8" t="n">
         <v>1648</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +749,15 @@
       <c r="D9" t="n">
         <v>848</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +774,15 @@
       <c r="D10" t="n">
         <v>1904</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +799,15 @@
       <c r="D11" t="n">
         <v>1320</v>
       </c>
-      <c r="E11" t="n">
-        <v>110</v>
-      </c>
-      <c r="F11" t="n">
-        <v>105</v>
-      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +824,23 @@
       <c r="D12" t="n">
         <v>604</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
         <v>81</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>28</v>
       </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +857,15 @@
       <c r="D13" t="n">
         <v>936</v>
       </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +882,15 @@
       <c r="D14" t="n">
         <v>1336</v>
       </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +907,23 @@
       <c r="D15" t="n">
         <v>1412</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
         <v>150</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>29</v>
       </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,12 +940,31 @@
       <c r="D16" t="n">
         <v>2816</v>
       </c>
-      <c r="E16" t="n">
-        <v>446</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F16" t="n">
-        <v>312</v>
-      </c>
+        <v>283</v>
+      </c>
+      <c r="G16" t="n">
+        <v>25</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>421</v>
+      </c>
+      <c r="J16" t="n">
+        <v>29</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -805,11 +981,38 @@
       <c r="D17" t="n">
         <v>6568</v>
       </c>
-      <c r="E17" t="n">
-        <v>918</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F17" t="n">
-        <v>812</v>
+        <v>1240</v>
+      </c>
+      <c r="G17" t="n">
+        <v>30</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>164</v>
+      </c>
+      <c r="J17" t="n">
+        <v>28</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>752</v>
+      </c>
+      <c r="M17" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="18">
@@ -827,12 +1030,23 @@
       <c r="D18" t="n">
         <v>3352</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
         <v>412</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>28</v>
       </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -849,12 +1063,15 @@
       <c r="D19" t="n">
         <v>628</v>
       </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -871,12 +1088,23 @@
       <c r="D20" t="n">
         <v>684</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
         <v>48</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>30</v>
       </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -893,12 +1121,15 @@
       <c r="D21" t="n">
         <v>568</v>
       </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -915,12 +1146,15 @@
       <c r="D22" t="n">
         <v>916</v>
       </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -937,12 +1171,23 @@
       <c r="D23" t="n">
         <v>2000</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
         <v>185</v>
       </c>
-      <c r="F23" t="n">
+      <c r="G23" t="n">
         <v>30</v>
       </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -959,12 +1204,23 @@
       <c r="D24" t="n">
         <v>1532</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
         <v>193</v>
       </c>
-      <c r="F24" t="n">
+      <c r="G24" t="n">
         <v>30</v>
       </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -981,12 +1237,23 @@
       <c r="D25" t="n">
         <v>1128</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
         <v>92</v>
       </c>
-      <c r="F25" t="n">
+      <c r="G25" t="n">
         <v>30</v>
       </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1003,12 +1270,31 @@
       <c r="D26" t="n">
         <v>1916</v>
       </c>
-      <c r="E26" t="n">
-        <v>355</v>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F26" t="n">
-        <v>182</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="G26" t="n">
+        <v>28</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>327</v>
+      </c>
+      <c r="J26" t="n">
+        <v>30</v>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1025,12 +1311,23 @@
       <c r="D27" t="n">
         <v>1524</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
         <v>234</v>
       </c>
-      <c r="F27" t="n">
+      <c r="G27" t="n">
         <v>25</v>
       </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1047,12 +1344,31 @@
       <c r="D28" t="n">
         <v>2816</v>
       </c>
-      <c r="E28" t="n">
-        <v>394</v>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F28" t="n">
-        <v>363</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="G28" t="n">
+        <v>25</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>338</v>
+      </c>
+      <c r="J28" t="n">
+        <v>28</v>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1069,12 +1385,23 @@
       <c r="D29" t="n">
         <v>468</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
         <v>47</v>
       </c>
-      <c r="F29" t="n">
+      <c r="G29" t="n">
         <v>28</v>
       </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1091,12 +1418,15 @@
       <c r="D30" t="n">
         <v>1040</v>
       </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1113,12 +1443,15 @@
       <c r="D31" t="n">
         <v>552</v>
       </c>
-      <c r="E31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1135,12 +1468,23 @@
       <c r="D32" t="n">
         <v>468</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
         <v>47</v>
       </c>
-      <c r="F32" t="n">
+      <c r="G32" t="n">
         <v>28</v>
       </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1157,12 +1501,23 @@
       <c r="D33" t="n">
         <v>2892</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
         <v>293</v>
       </c>
-      <c r="F33" t="n">
+      <c r="G33" t="n">
         <v>29</v>
       </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1179,12 +1534,15 @@
       <c r="D34" t="n">
         <v>952</v>
       </c>
-      <c r="E34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1201,12 +1559,31 @@
       <c r="D35" t="n">
         <v>1268</v>
       </c>
-      <c r="E35" t="n">
-        <v>248</v>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F35" t="n">
-        <v>126</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="G35" t="n">
+        <v>28</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>98</v>
+      </c>
+      <c r="J35" t="n">
+        <v>29</v>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1223,12 +1600,31 @@
       <c r="D36" t="n">
         <v>2044</v>
       </c>
-      <c r="E36" t="n">
-        <v>355</v>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F36" t="n">
-        <v>214</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="G36" t="n">
+        <v>29</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>326</v>
+      </c>
+      <c r="J36" t="n">
+        <v>29</v>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1245,12 +1641,23 @@
       <c r="D37" t="n">
         <v>1132</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
         <v>157</v>
       </c>
-      <c r="F37" t="n">
+      <c r="G37" t="n">
         <v>29</v>
       </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
